--- a/exel/planilha_teste.xlsx
+++ b/exel/planilha_teste.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SENAI\Desktop\teste_media\exel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7018AF95-A69B-4ACE-BDC5-FCFF13988578}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{143F7EEE-92D4-4071-A6C5-39CA7DB4E310}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12225" xr2:uid="{1EDEA423-077C-400A-B5D6-EFC6C4C997AF}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12225" activeTab="1" xr2:uid="{1EDEA423-077C-400A-B5D6-EFC6C4C997AF}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
+    <sheet name="Planilha1 (2)" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="49">
   <si>
     <t>TIPO DE TESTE</t>
   </si>
@@ -106,13 +107,79 @@
   </si>
   <si>
     <t>Testando com um valor maior que 10</t>
+  </si>
+  <si>
+    <t>boletim.calculos</t>
+  </si>
+  <si>
+    <t>calcular_media</t>
+  </si>
+  <si>
+    <t>Teste com nota inteiras</t>
+  </si>
+  <si>
+    <t>[8,10]</t>
+  </si>
+  <si>
+    <t>unitario</t>
+  </si>
+  <si>
+    <t>Teste com nota decimais</t>
+  </si>
+  <si>
+    <t>9.0</t>
+  </si>
+  <si>
+    <t>[2.9,7.8]</t>
+  </si>
+  <si>
+    <t>5.3</t>
+  </si>
+  <si>
+    <t>Teste com um número</t>
+  </si>
+  <si>
+    <t>[9]</t>
+  </si>
+  <si>
+    <t>Teste com números inteiros e decimais</t>
+  </si>
+  <si>
+    <t>[4,9,6.5]</t>
+  </si>
+  <si>
+    <t>6.5</t>
+  </si>
+  <si>
+    <t>Teste com mais de 10 números</t>
+  </si>
+  <si>
+    <t>[9,1,5,8.5,7.3,9,10,3.2,5.7,3,9]</t>
+  </si>
+  <si>
+    <t>6.4</t>
+  </si>
+  <si>
+    <t>Teste com números negativos</t>
+  </si>
+  <si>
+    <t>[-9,8]</t>
+  </si>
+  <si>
+    <t>Número inválido, apenas números acima de 0</t>
+  </si>
+  <si>
+    <t>Teste com números igual a 0</t>
+  </si>
+  <si>
+    <t>[0]</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -128,8 +195,19 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -172,6 +250,24 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9900CC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC66FF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC99FF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="15">
     <border>
@@ -361,7 +457,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -449,6 +545,60 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -458,6 +608,9 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFCC99FF"/>
+      <color rgb="FFCC66FF"/>
+      <color rgb="FF9900CC"/>
       <color rgb="FFF89090"/>
       <color rgb="FFF56565"/>
       <color rgb="FFF8CFCC"/>
@@ -1056,4 +1209,250 @@
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB947121-80F8-41F2-93BF-E1CC24257DA2}">
+  <dimension ref="A1:I31"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="52" customWidth="1"/>
+    <col min="5" max="5" width="15.7109375" customWidth="1"/>
+    <col min="6" max="6" width="64.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="32" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="33" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="32" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="33" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" s="35" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" s="35" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" s="35" t="s">
+        <v>29</v>
+      </c>
+      <c r="E2" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="F2" s="37" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="47" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="48" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" s="48" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" s="41" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" s="42" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3" s="43" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" s="35" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="35" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="39" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" s="40" t="s">
+        <v>37</v>
+      </c>
+      <c r="F4" s="38" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="47" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="48" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="48" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="45" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5" s="46" t="s">
+        <v>39</v>
+      </c>
+      <c r="F5" s="44" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="35" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="35" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="39" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="F6" s="38" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="47" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" s="48" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="48" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="45" t="s">
+        <v>44</v>
+      </c>
+      <c r="E7" s="49" t="s">
+        <v>45</v>
+      </c>
+      <c r="F7" s="44" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" s="35" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="35" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="39" t="s">
+        <v>47</v>
+      </c>
+      <c r="E8" s="40" t="s">
+        <v>48</v>
+      </c>
+      <c r="F8" s="38" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="47" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" s="48" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="48" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="45"/>
+      <c r="E9" s="46"/>
+      <c r="F9" s="44"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D10" s="3"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="B13" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="D13" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="E13" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="F13" s="23" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="19"/>
+      <c r="B14" s="20"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="29"/>
+      <c r="F14" s="22"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="16"/>
+      <c r="B15" s="17"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="30"/>
+      <c r="F15" s="18"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="14"/>
+      <c r="B16" s="15"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="31"/>
+      <c r="F16" s="14"/>
+    </row>
+    <row r="19" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="E19" s="21"/>
+    </row>
+    <row r="20" spans="5:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="I31" s="24"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>